--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_maule.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_maule.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:47</t>
+    <t xml:space="preserve">2026-09-09 20:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_maule.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_maule.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:52</t>
+    <t xml:space="preserve">2026-09-18 10:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -1107,12 +1107,12 @@
         <v>28</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>34.86</v>
+        <v>29.02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -1121,12 +1121,12 @@
         <v>29</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>62.31</v>
+        <v>63.17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
@@ -1135,12 +1135,12 @@
         <v>30</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>94.39</v>
+        <v>93.27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>3</v>
@@ -1149,12 +1149,12 @@
         <v>28</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>33.91</v>
+        <v>34.86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>3</v>
@@ -1163,12 +1163,12 @@
         <v>29</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>66.36</v>
+        <v>62.31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>3</v>
@@ -1177,12 +1177,12 @@
         <v>30</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>93.3</v>
+        <v>94.39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>3</v>
@@ -1191,12 +1191,12 @@
         <v>28</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>30.62</v>
+        <v>33.91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>3</v>
@@ -1205,12 +1205,12 @@
         <v>29</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>67.67</v>
+        <v>66.36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>3</v>
@@ -1219,12 +1219,12 @@
         <v>30</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>96.11</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>3</v>
@@ -1233,12 +1233,12 @@
         <v>28</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>29.02</v>
+        <v>30.62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>3</v>
@@ -1247,12 +1247,12 @@
         <v>29</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>63.17</v>
+        <v>67.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>3</v>
@@ -1261,12 +1261,12 @@
         <v>30</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>93.27</v>
+        <v>96.11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
@@ -1275,12 +1275,12 @@
         <v>31</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>94.54</v>
+        <v>94.85</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>8</v>
@@ -1289,12 +1289,12 @@
         <v>32</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>98.32</v>
+        <v>96.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>8</v>
@@ -1303,12 +1303,12 @@
         <v>31</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>94.34</v>
+        <v>94.54</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -1317,12 +1317,12 @@
         <v>32</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>96.44</v>
+        <v>98.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>8</v>
@@ -1331,12 +1331,12 @@
         <v>31</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>95.26</v>
+        <v>94.34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>8</v>
@@ -1345,12 +1345,12 @@
         <v>32</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>97.8</v>
+        <v>96.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>8</v>
@@ -1359,12 +1359,12 @@
         <v>31</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>94.85</v>
+        <v>95.26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>8</v>
@@ -1373,12 +1373,12 @@
         <v>32</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>96.87</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>9</v>
@@ -1387,12 +1387,12 @@
         <v>33</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>91.34</v>
+        <v>90.86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>9</v>
@@ -1401,12 +1401,12 @@
         <v>34</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>88.66</v>
+        <v>87.96</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>9</v>
@@ -1415,12 +1415,12 @@
         <v>33</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>90.44</v>
+        <v>91.34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>9</v>
@@ -1429,12 +1429,12 @@
         <v>34</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>88.15</v>
+        <v>88.66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>9</v>
@@ -1443,12 +1443,12 @@
         <v>33</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>88.67</v>
+        <v>90.44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>9</v>
@@ -1457,12 +1457,12 @@
         <v>34</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>86.61</v>
+        <v>88.15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>9</v>
@@ -1471,12 +1471,12 @@
         <v>33</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>90.86</v>
+        <v>88.67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>9</v>
@@ -1485,7 +1485,7 @@
         <v>34</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>87.96</v>
+        <v>86.61</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_maule.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_maule.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:43</t>
+    <t xml:space="preserve">2026-09-23 16:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_maule.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_maule.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 16:26</t>
+    <t xml:space="preserve">2026-10-05 06:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
